--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6020,0.1675,0.0028,0.0806</t>
-  </si>
-  <si>
-    <t>0.0212,0.0001,0.0016,0.9911</t>
-  </si>
-  <si>
-    <t>0.6003,0.2140,0.0164,0.1249</t>
-  </si>
-  <si>
-    <t>0.0715,0.0033,0.0030,0.9793</t>
-  </si>
-  <si>
-    <t>0.9954,0.0038,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0109,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9356,0.0471,0.0282,0.0015</t>
-  </si>
-  <si>
-    <t>0.9770,0.0282,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.9856,0.0096,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.9899,0.0142,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0059,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8348,0.1060,0.0385,0.0099</t>
-  </si>
-  <si>
-    <t>0.1121,0.0333,0.8797,0.0050</t>
-  </si>
-  <si>
-    <t>0.1507,0.0279,0.8635,0.0054</t>
-  </si>
-  <si>
-    <t>0.1657,0.0878,0.7437,0.0126</t>
-  </si>
-  <si>
-    <t>0.8016,0.0485,0.1711,0.0124</t>
-  </si>
-  <si>
-    <t>0.0572,0.9641,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0729,0.9537,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.4266,0.6252,0.0294,0.0012</t>
-  </si>
-  <si>
-    <t>0.1089,0.9140,0.0051,0.0013</t>
-  </si>
-  <si>
-    <t>0.0305,0.9748,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.5730,0.0207,0.5855,0.0064</t>
-  </si>
-  <si>
-    <t>0.1181,0.0204,0.8817,0.0039</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.9918,0.0278</t>
-  </si>
-  <si>
-    <t>0.1544,0.0556,0.7762,0.0022</t>
-  </si>
-  <si>
-    <t>0.2812,0.0467,0.7143,0.0063</t>
-  </si>
-  <si>
-    <t>0.0218,0.0008,0.9794,0.0105</t>
-  </si>
-  <si>
-    <t>0.0080,0.0015,0.9827,0.0286</t>
-  </si>
-  <si>
-    <t>0.5188,0.5584,0.0198,0.0008</t>
-  </si>
-  <si>
-    <t>0.1018,0.2787,0.7224,0.0036</t>
-  </si>
-  <si>
-    <t>0.0054,0.0489,0.9816,0.0028</t>
-  </si>
-  <si>
-    <t>0.0063,0.9668,0.0999,0.0004</t>
-  </si>
-  <si>
-    <t>0.7775,0.2336,0.0148,0.0122</t>
-  </si>
-  <si>
-    <t>0.7107,0.2520,0.0889,0.0065</t>
-  </si>
-  <si>
-    <t>0.4093,0.6155,0.0362,0.0009</t>
-  </si>
-  <si>
-    <t>0.0844,0.9053,0.0684,0.0010</t>
-  </si>
-  <si>
-    <t>0.0455,0.8926,0.0447,0.0070</t>
-  </si>
-  <si>
-    <t>0.0942,0.0291,0.8776,0.0205</t>
-  </si>
-  <si>
-    <t>0.0198,0.3438,0.8611,0.0393</t>
-  </si>
-  <si>
-    <t>0.1735,0.0268,0.8219,0.0205</t>
-  </si>
-  <si>
-    <t>0.0111,0.1103,0.9362,0.0012</t>
-  </si>
-  <si>
-    <t>0.0156,0.9506,0.0806,0.0003</t>
-  </si>
-  <si>
-    <t>0.0158,0.0570,0.9457,0.0162</t>
-  </si>
-  <si>
-    <t>0.1938,0.5772,0.0246,0.4090</t>
-  </si>
-  <si>
-    <t>0.0099,0.9638,0.0515,0.0127</t>
-  </si>
-  <si>
-    <t>0.0035,0.9729,0.1749,0.0004</t>
-  </si>
-  <si>
-    <t>0.0039,0.9791,0.0067,0.0111</t>
-  </si>
-  <si>
-    <t>0.0060,0.4047,0.9538,0.0031</t>
-  </si>
-  <si>
-    <t>0.0031,0.3009,0.9681,0.0011</t>
-  </si>
-  <si>
-    <t>0.1920,0.0142,0.8441,0.0128</t>
-  </si>
-  <si>
-    <t>0.0551,0.0209,0.9291,0.0078</t>
-  </si>
-  <si>
-    <t>0.0202,0.0288,0.9683,0.0014</t>
-  </si>
-  <si>
-    <t>0.0064,0.0139,0.9848,0.0006</t>
-  </si>
-  <si>
-    <t>0.7844,0.3518,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.9676,0.0299,0.0092,0.0013</t>
-  </si>
-  <si>
-    <t>0.9628,0.0207,0.0038,0.0045</t>
-  </si>
-  <si>
-    <t>0.0149,0.1003,0.9745,0.0061</t>
-  </si>
-  <si>
-    <t>0.9812,0.0317,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9618,0.0553,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.8919,0.1791,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.9082,0.8186,0.0011</t>
-  </si>
-  <si>
-    <t>0.0081,0.2713,0.9654,0.0024</t>
-  </si>
-  <si>
-    <t>0.0197,0.1854,0.9418,0.0084</t>
-  </si>
-  <si>
-    <t>0.0002,0.9475,0.9588,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0142,0.9944,0.0007</t>
-  </si>
-  <si>
-    <t>0.1325,0.8414,0.0959,0.0031</t>
-  </si>
-  <si>
-    <t>0.0116,0.9869,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9446,0.0167,0.0405,0.0041</t>
-  </si>
-  <si>
-    <t>0.1541,0.2093,0.6785,0.0044</t>
-  </si>
-  <si>
-    <t>0.0073,0.0512,0.9860,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.7959,0.9368,0.0007</t>
-  </si>
-  <si>
-    <t>0.0069,0.9259,0.3156,0.0014</t>
-  </si>
-  <si>
-    <t>0.0015,0.9888,0.1120,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.8895,0.9289,0.0002</t>
-  </si>
-  <si>
-    <t>0.0911,0.0056,0.0056,0.9609</t>
-  </si>
-  <si>
-    <t>0.0022,0.0213,0.0020,0.9973</t>
-  </si>
-  <si>
-    <t>0.0485,0.0022,0.0017,0.9814</t>
-  </si>
-  <si>
-    <t>0.1605,0.0223,0.0115,0.9005</t>
-  </si>
-  <si>
-    <t>0.0277,0.0073,0.0119,0.9786</t>
-  </si>
-  <si>
-    <t>0.0157,0.0147,0.0029,0.9905</t>
-  </si>
-  <si>
-    <t>0.0021,0.9597,0.6840,0.0005</t>
-  </si>
-  <si>
-    <t>0.0015,0.7988,0.9552,0.0002</t>
-  </si>
-  <si>
-    <t>0.0163,0.8906,0.3064,0.0014</t>
-  </si>
-  <si>
-    <t>0.0036,0.6871,0.9001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.9315,0.9701,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.7976,0.7829,0.0012</t>
-  </si>
-  <si>
-    <t>0.9939,0.0067,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9475,0.0765,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9832,0.0160,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0021,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9823,0.0221,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9934,0.0073,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0050,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9751,0.0276,0.0046,0.0011</t>
-  </si>
-  <si>
-    <t>0.9968,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9968,0.0035,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0022,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9972,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0045,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0016,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9855,0.0196,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0028,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.0017,0.9884,0.0164</t>
-  </si>
-  <si>
-    <t>0.0513,0.0596,0.8987,0.0047</t>
-  </si>
-  <si>
-    <t>0.6819,0.0249,0.1118,0.1504</t>
-  </si>
-  <si>
-    <t>0.0123,0.0303,0.9725,0.0011</t>
-  </si>
-  <si>
-    <t>0.1312,0.9251,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0633,0.9511,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.0753,0.9399,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.4851,0.6814,0.0034,0.0012</t>
-  </si>
-  <si>
-    <t>0.3389,0.7685,0.0104,0.0015</t>
-  </si>
-  <si>
-    <t>0.0056,0.9908,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.7722,0.3060,0.0129,0.0011</t>
-  </si>
-  <si>
-    <t>0.4208,0.2953,0.3399,0.0141</t>
-  </si>
-  <si>
-    <t>0.2029,0.0381,0.8082,0.0015</t>
-  </si>
-  <si>
-    <t>0.3041,0.5172,0.1523,0.0057</t>
-  </si>
-  <si>
-    <t>0.6375,0.1951,0.2311,0.0121</t>
-  </si>
-  <si>
-    <t>0.1903,0.1246,0.2720,0.5938</t>
-  </si>
-  <si>
-    <t>0.0075,0.9760,0.0161,0.0051</t>
-  </si>
-  <si>
-    <t>0.0028,0.9834,0.0043,0.0157</t>
-  </si>
-  <si>
-    <t>0.0380,0.7895,0.2235,0.1080</t>
-  </si>
-  <si>
-    <t>0.0035,0.9351,0.8342,0.0021</t>
-  </si>
-  <si>
-    <t>0.0379,0.9596,0.0320,0.0001</t>
-  </si>
-  <si>
-    <t>0.5848,0.4360,0.0349,0.0007</t>
-  </si>
-  <si>
-    <t>0.5833,0.6011,0.0055,0.0006</t>
-  </si>
-  <si>
-    <t>0.9712,0.0241,0.0061,0.0010</t>
-  </si>
-  <si>
-    <t>0.9559,0.0344,0.0024,0.0034</t>
-  </si>
-  <si>
-    <t>0.9889,0.0013,0.0003,0.0039</t>
-  </si>
-  <si>
-    <t>0.9839,0.0061,0.0023,0.0019</t>
-  </si>
-  <si>
-    <t>0.9940,0.0014,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.8888,0.0286,0.1154,0.0016</t>
-  </si>
-  <si>
-    <t>0.9751,0.0152,0.0039,0.0020</t>
-  </si>
-  <si>
-    <t>0.9605,0.0297,0.0150,0.0014</t>
-  </si>
-  <si>
-    <t>0.0033,0.8263,0.7991,0.0011</t>
-  </si>
-  <si>
-    <t>0.0034,0.9012,0.7434,0.0009</t>
-  </si>
-  <si>
-    <t>0.0011,0.7652,0.9137,0.0001</t>
-  </si>
-  <si>
-    <t>0.0250,0.1106,0.9059,0.0033</t>
-  </si>
-  <si>
-    <t>0.8694,0.0603,0.0664,0.0147</t>
-  </si>
-  <si>
-    <t>0.6786,0.0926,0.3308,0.0087</t>
-  </si>
-  <si>
-    <t>0.0564,0.0025,0.9604,0.0110</t>
-  </si>
-  <si>
-    <t>0.7958,0.0617,0.0972,0.0200</t>
-  </si>
-  <si>
-    <t>0.0068,0.0153,0.0014,0.9953</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0019,0.9996</t>
-  </si>
-  <si>
-    <t>0.0048,0.0106,0.0011,0.9969</t>
-  </si>
-  <si>
-    <t>0.0320,0.0001,0.0323,0.9567</t>
-  </si>
-  <si>
-    <t>0.0023,0.9249,0.5847,0.0007</t>
-  </si>
-  <si>
-    <t>0.9749,0.0212,0.0020,0.0017</t>
-  </si>
-  <si>
-    <t>0.5137,0.6136,0.0102,0.0031</t>
-  </si>
-  <si>
-    <t>0.9877,0.0041,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.7051,0.4412,0.0067,0.0020</t>
-  </si>
-  <si>
-    <t>0.9563,0.0025,0.0116,0.0137</t>
-  </si>
-  <si>
-    <t>0.7388,0.0325,0.2297,0.0474</t>
-  </si>
-  <si>
-    <t>0.9390,0.0548,0.0019,0.0041</t>
-  </si>
-  <si>
-    <t>0.0052,0.3057,0.9162,0.0158</t>
-  </si>
-  <si>
-    <t>0.8964,0.0069,0.0287,0.0435</t>
-  </si>
-  <si>
-    <t>0.8948,0.0118,0.0570,0.0275</t>
-  </si>
-  <si>
-    <t>0.3308,0.7518,0.0107,0.0046</t>
-  </si>
-  <si>
-    <t>0.7133,0.3017,0.0348,0.0097</t>
-  </si>
-  <si>
-    <t>0.6220,0.4517,0.0341,0.0049</t>
-  </si>
-  <si>
-    <t>0.3363,0.7095,0.0124,0.0116</t>
-  </si>
-  <si>
-    <t>0.6485,0.3009,0.0899,0.0016</t>
-  </si>
-  <si>
-    <t>0.6843,0.3867,0.0370,0.0049</t>
-  </si>
-  <si>
-    <t>0.9766,0.0137,0.0041,0.0019</t>
-  </si>
-  <si>
-    <t>0.9942,0.0018,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9941,0.0046,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0037,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9834,0.0047,0.0034,0.0022</t>
-  </si>
-  <si>
-    <t>0.9889,0.0091,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9754,0.0128,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.9934,0.0033,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.3118,0.7630,0.0315,0.0035</t>
-  </si>
-  <si>
-    <t>0.4016,0.6432,0.0229,0.0020</t>
-  </si>
-  <si>
-    <t>0.5675,0.5559,0.0116,0.0007</t>
-  </si>
-  <si>
-    <t>0.9128,0.0599,0.0471,0.0041</t>
-  </si>
-  <si>
-    <t>0.9442,0.1060,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9790,0.0138,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.8957,0.1372,0.0089,0.0018</t>
-  </si>
-  <si>
-    <t>0.9067,0.0842,0.0151,0.0043</t>
-  </si>
-  <si>
-    <t>0.0038,0.0254,0.9922,0.0005</t>
-  </si>
-  <si>
-    <t>0.9694,0.0140,0.0108,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.0042,0.9965,0.0004</t>
-  </si>
-  <si>
-    <t>0.0088,0.3424,0.9270,0.0012</t>
-  </si>
-  <si>
-    <t>0.0353,0.0019,0.9709,0.0063</t>
-  </si>
-  <si>
-    <t>0.0077,0.0335,0.9786,0.0021</t>
-  </si>
-  <si>
-    <t>0.0505,0.0643,0.9196,0.0058</t>
-  </si>
-  <si>
-    <t>0.0185,0.0118,0.9684,0.0010</t>
-  </si>
-  <si>
-    <t>0.0491,0.0150,0.9318,0.0149</t>
-  </si>
-  <si>
-    <t>0.1036,0.0909,0.8299,0.0100</t>
-  </si>
-  <si>
-    <t>0.0335,0.0337,0.9524,0.0020</t>
-  </si>
-  <si>
-    <t>0.5249,0.1656,0.3962,0.0330</t>
-  </si>
-  <si>
-    <t>0.2412,0.1021,0.6271,0.0047</t>
-  </si>
-  <si>
-    <t>0.0506,0.0465,0.9238,0.0032</t>
-  </si>
-  <si>
-    <t>0.5028,0.1506,0.4053,0.0169</t>
-  </si>
-  <si>
-    <t>0.5970,0.0786,0.4174,0.0059</t>
-  </si>
-  <si>
-    <t>0.1451,0.0250,0.8596,0.0067</t>
-  </si>
-  <si>
-    <t>0.6524,0.4776,0.0123,0.0005</t>
-  </si>
-  <si>
-    <t>0.6290,0.3872,0.0312,0.0029</t>
-  </si>
-  <si>
-    <t>0.5965,0.3832,0.0336,0.0003</t>
-  </si>
-  <si>
-    <t>0.9780,0.0327,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9353,0.1231,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.4100,0.3637,0.3337,0.0367</t>
-  </si>
-  <si>
-    <t>0.8971,0.0185,0.1036,0.0042</t>
-  </si>
-  <si>
-    <t>0.8541,0.0623,0.0316,0.0229</t>
-  </si>
-  <si>
-    <t>0.4958,0.2867,0.3433,0.0376</t>
-  </si>
-  <si>
-    <t>0.4930,0.0461,0.5836,0.0044</t>
-  </si>
-  <si>
-    <t>0.0100,0.0075,0.9781,0.0151</t>
-  </si>
-  <si>
-    <t>0.0563,0.4243,0.7185,0.0274</t>
-  </si>
-  <si>
-    <t>0.0152,0.2796,0.8978,0.0059</t>
-  </si>
-  <si>
-    <t>0.2072,0.0937,0.6691,0.0119</t>
-  </si>
-  <si>
-    <t>0.0690,0.0491,0.8943,0.0017</t>
-  </si>
-  <si>
-    <t>0.9491,0.0817,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9925,0.0080,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9842,0.0071,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.9835,0.0161,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9846,0.0310,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0018,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9904,0.0060,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9630,0.0474,0.0051,0.0009</t>
-  </si>
-  <si>
-    <t>0.0243,0.0321,0.9557,0.0053</t>
-  </si>
-  <si>
-    <t>0.0491,0.4641,0.7089,0.0072</t>
-  </si>
-  <si>
-    <t>0.6315,0.4006,0.0631,0.0202</t>
-  </si>
-  <si>
-    <t>0.0021,0.0480,0.9776,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0046,0.9919,0.0065</t>
-  </si>
-  <si>
-    <t>0.0459,0.1339,0.8324,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.0053,0.9960,0.0007</t>
-  </si>
-  <si>
-    <t>0.0362,0.0718,0.8479,0.0098</t>
-  </si>
-  <si>
-    <t>0.0022,0.0559,0.9896,0.0007</t>
-  </si>
-  <si>
-    <t>0.0307,0.1349,0.8931,0.0098</t>
-  </si>
-  <si>
-    <t>0.1387,0.0171,0.8777,0.0088</t>
-  </si>
-  <si>
-    <t>0.4054,0.0086,0.4410,0.1979</t>
-  </si>
-  <si>
-    <t>0.4934,0.0069,0.6764,0.0120</t>
-  </si>
-  <si>
-    <t>0.8165,0.0487,0.1301,0.0133</t>
-  </si>
-  <si>
-    <t>0.9884,0.0188,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9930,0.0039,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9839,0.0168,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9829,0.0153,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.9948,0.0026,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9886,0.0127,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9883,0.0107,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9955,0.0026,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.1595,0.0822,0.7219,0.0023</t>
-  </si>
-  <si>
-    <t>0.0005,0.1948,0.9914,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.0166,0.9751,0.0091</t>
-  </si>
-  <si>
-    <t>0.0827,0.0099,0.9245,0.0036</t>
-  </si>
-  <si>
-    <t>0.0015,0.0036,0.9914,0.0033</t>
-  </si>
-  <si>
-    <t>0.4126,0.0297,0.5982,0.0466</t>
-  </si>
-  <si>
-    <t>0.0704,0.0157,0.9251,0.0037</t>
-  </si>
-  <si>
-    <t>0.0042,0.0060,0.9674,0.0632</t>
-  </si>
-  <si>
-    <t>0.6014,0.0039,0.0095,0.4672</t>
-  </si>
-  <si>
-    <t>0.2233,0.1008,0.0172,0.8043</t>
-  </si>
-  <si>
-    <t>0.0500,0.0030,0.0078,0.9740</t>
-  </si>
-  <si>
-    <t>0.0093,0.0003,0.0066,0.9915</t>
-  </si>
-  <si>
-    <t>0.0006,0.0022,0.0156,0.9972</t>
-  </si>
-  <si>
-    <t>0.6445,0.0345,0.0473,0.2765</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7042,0.2158,0.0946,0.0383</t>
+  </si>
+  <si>
+    <t>0.0183,0.0007,0.0025,0.9924</t>
+  </si>
+  <si>
+    <t>0.7200,0.0275,0.0039,0.2307</t>
+  </si>
+  <si>
+    <t>0.0314,0.0241,0.0040,0.9833</t>
+  </si>
+  <si>
+    <t>0.9899,0.0077,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0033,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9886,0.0145,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9830,0.0156,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.9820,0.0174,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9754,0.0289,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9900,0.0133,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.8144,0.1045,0.0907,0.0032</t>
+  </si>
+  <si>
+    <t>0.4498,0.0610,0.5918,0.0065</t>
+  </si>
+  <si>
+    <t>0.2801,0.0521,0.7571,0.0042</t>
+  </si>
+  <si>
+    <t>0.1313,0.0289,0.8589,0.0113</t>
+  </si>
+  <si>
+    <t>0.5861,0.0613,0.4826,0.0110</t>
+  </si>
+  <si>
+    <t>0.0606,0.9542,0.0060,0.0004</t>
+  </si>
+  <si>
+    <t>0.1806,0.8995,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.6430,0.5072,0.0124,0.0010</t>
+  </si>
+  <si>
+    <t>0.0946,0.9297,0.0081,0.0004</t>
+  </si>
+  <si>
+    <t>0.0456,0.9679,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.7196,0.0096,0.2513,0.0363</t>
+  </si>
+  <si>
+    <t>0.3399,0.0089,0.6893,0.0330</t>
+  </si>
+  <si>
+    <t>0.0149,0.0033,0.9813,0.0031</t>
+  </si>
+  <si>
+    <t>0.1890,0.0320,0.7947,0.0041</t>
+  </si>
+  <si>
+    <t>0.2218,0.0107,0.8642,0.0052</t>
+  </si>
+  <si>
+    <t>0.1032,0.0064,0.9365,0.0055</t>
+  </si>
+  <si>
+    <t>0.0046,0.0015,0.9910,0.0033</t>
+  </si>
+  <si>
+    <t>0.5569,0.6268,0.0049,0.0007</t>
+  </si>
+  <si>
+    <t>0.4944,0.4607,0.0910,0.0018</t>
+  </si>
+  <si>
+    <t>0.0026,0.0188,0.9905,0.0024</t>
+  </si>
+  <si>
+    <t>0.0240,0.9364,0.0694,0.0012</t>
+  </si>
+  <si>
+    <t>0.6768,0.3710,0.0225,0.0112</t>
+  </si>
+  <si>
+    <t>0.6335,0.4296,0.0328,0.0047</t>
+  </si>
+  <si>
+    <t>0.8208,0.2602,0.0089,0.0005</t>
+  </si>
+  <si>
+    <t>0.0365,0.9419,0.0555,0.0004</t>
+  </si>
+  <si>
+    <t>0.0138,0.4546,0.7458,0.0432</t>
+  </si>
+  <si>
+    <t>0.0723,0.0545,0.8384,0.0874</t>
+  </si>
+  <si>
+    <t>0.0187,0.6407,0.6608,0.0115</t>
+  </si>
+  <si>
+    <t>0.0310,0.0301,0.9387,0.0214</t>
+  </si>
+  <si>
+    <t>0.0164,0.0413,0.9591,0.0064</t>
+  </si>
+  <si>
+    <t>0.0118,0.9356,0.0921,0.0002</t>
+  </si>
+  <si>
+    <t>0.0117,0.3129,0.9135,0.0077</t>
+  </si>
+  <si>
+    <t>0.4820,0.1974,0.1779,0.3345</t>
+  </si>
+  <si>
+    <t>0.0141,0.9641,0.0048,0.0176</t>
+  </si>
+  <si>
+    <t>0.0065,0.9725,0.0442,0.0059</t>
+  </si>
+  <si>
+    <t>0.0025,0.9841,0.0756,0.0011</t>
+  </si>
+  <si>
+    <t>0.0072,0.0421,0.9566,0.0118</t>
+  </si>
+  <si>
+    <t>0.0032,0.6277,0.9548,0.0006</t>
+  </si>
+  <si>
+    <t>0.1423,0.0192,0.8726,0.0205</t>
+  </si>
+  <si>
+    <t>0.1418,0.0072,0.8702,0.0354</t>
+  </si>
+  <si>
+    <t>0.0005,0.1024,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9962,0.0054</t>
+  </si>
+  <si>
+    <t>0.9249,0.1099,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.9177,0.0646,0.0281,0.0037</t>
+  </si>
+  <si>
+    <t>0.9877,0.0096,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.0088,0.0594,0.9744,0.0101</t>
+  </si>
+  <si>
+    <t>0.9797,0.0206,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.9856,0.0114,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9146,0.1665,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.9569,0.8729,0.0001</t>
+  </si>
+  <si>
+    <t>0.0140,0.2950,0.9283,0.0033</t>
+  </si>
+  <si>
+    <t>0.0292,0.0532,0.9245,0.0111</t>
+  </si>
+  <si>
+    <t>0.0025,0.8608,0.7442,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0095,0.9957,0.0012</t>
+  </si>
+  <si>
+    <t>0.0535,0.9335,0.0124,0.0012</t>
+  </si>
+  <si>
+    <t>0.0339,0.9654,0.0147,0.0002</t>
+  </si>
+  <si>
+    <t>0.8730,0.0511,0.1012,0.0054</t>
+  </si>
+  <si>
+    <t>0.7575,0.1201,0.2084,0.0074</t>
+  </si>
+  <si>
+    <t>0.0194,0.0559,0.9701,0.0024</t>
+  </si>
+  <si>
+    <t>0.0004,0.9214,0.9153,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.8596,0.7880,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9782,0.3981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9657,0.9145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0674,0.0300,0.0248,0.9492</t>
+  </si>
+  <si>
+    <t>0.0035,0.0251,0.0008,0.9969</t>
+  </si>
+  <si>
+    <t>0.0084,0.0229,0.0010,0.9943</t>
+  </si>
+  <si>
+    <t>0.0311,0.0019,0.0039,0.9860</t>
+  </si>
+  <si>
+    <t>0.0276,0.0015,0.0031,0.9885</t>
+  </si>
+  <si>
+    <t>0.0079,0.0105,0.0043,0.9925</t>
+  </si>
+  <si>
+    <t>0.0028,0.9666,0.3551,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.8566,0.9535,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.8944,0.3134,0.0010</t>
+  </si>
+  <si>
+    <t>0.0059,0.5099,0.9063,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.9679,0.8724,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9372,0.8621,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0051,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9514,0.0607,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9721,0.0382,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9883,0.0123,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9874,0.0276,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0034,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9620,0.0489,0.0061,0.0006</t>
+  </si>
+  <si>
+    <t>0.9522,0.0521,0.0069,0.0018</t>
+  </si>
+  <si>
+    <t>0.9943,0.0014,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9952,0.0044,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0055,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0077,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0035,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0070,0.0044,0.9853,0.0040</t>
+  </si>
+  <si>
+    <t>0.0331,0.0145,0.9387,0.0197</t>
+  </si>
+  <si>
+    <t>0.8211,0.0064,0.0797,0.0594</t>
+  </si>
+  <si>
+    <t>0.2355,0.0730,0.6789,0.0047</t>
+  </si>
+  <si>
+    <t>0.2610,0.7934,0.0132,0.0022</t>
+  </si>
+  <si>
+    <t>0.0672,0.9471,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.2277,0.8573,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.0609,0.9470,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0413,0.9708,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0118,0.9836,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.4477,0.7372,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.7035,0.1029,0.2648,0.0313</t>
+  </si>
+  <si>
+    <t>0.0797,0.0274,0.9195,0.0041</t>
+  </si>
+  <si>
+    <t>0.5948,0.1949,0.2029,0.0754</t>
+  </si>
+  <si>
+    <t>0.4871,0.4269,0.1349,0.0119</t>
+  </si>
+  <si>
+    <t>0.3007,0.1060,0.2882,0.4911</t>
+  </si>
+  <si>
+    <t>0.0035,0.9879,0.0134,0.0014</t>
+  </si>
+  <si>
+    <t>0.0323,0.9219,0.1232,0.0051</t>
+  </si>
+  <si>
+    <t>0.0490,0.8861,0.0209,0.0435</t>
+  </si>
+  <si>
+    <t>0.0016,0.9247,0.8472,0.0016</t>
+  </si>
+  <si>
+    <t>0.1271,0.8883,0.0312,0.0005</t>
+  </si>
+  <si>
+    <t>0.4736,0.6621,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.4942,0.5135,0.0424,0.0010</t>
+  </si>
+  <si>
+    <t>0.9789,0.0257,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9852,0.0106,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0020,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9849,0.0138,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9839,0.0154,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.7782,0.0893,0.1036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9804,0.0115,0.0061,0.0010</t>
+  </si>
+  <si>
+    <t>0.9793,0.0157,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.0089,0.6659,0.8479,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.9068,0.7448,0.0002</t>
+  </si>
+  <si>
+    <t>0.0203,0.7047,0.5739,0.0021</t>
+  </si>
+  <si>
+    <t>0.0239,0.4833,0.7124,0.0018</t>
+  </si>
+  <si>
+    <t>0.6625,0.2610,0.0813,0.0117</t>
+  </si>
+  <si>
+    <t>0.4734,0.1549,0.3213,0.0035</t>
+  </si>
+  <si>
+    <t>0.3143,0.0237,0.7504,0.0283</t>
+  </si>
+  <si>
+    <t>0.4097,0.2141,0.4628,0.0886</t>
+  </si>
+  <si>
+    <t>0.1733,0.0041,0.0035,0.9356</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.0027,0.9996</t>
+  </si>
+  <si>
+    <t>0.0164,0.0017,0.0012,0.9939</t>
+  </si>
+  <si>
+    <t>0.0136,0.0010,0.0388,0.9769</t>
+  </si>
+  <si>
+    <t>0.0017,0.6384,0.9282,0.0010</t>
+  </si>
+  <si>
+    <t>0.8615,0.1993,0.0088,0.0011</t>
+  </si>
+  <si>
+    <t>0.2027,0.8248,0.0177,0.0035</t>
+  </si>
+  <si>
+    <t>0.9692,0.0178,0.0037,0.0023</t>
+  </si>
+  <si>
+    <t>0.4659,0.7202,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.8086,0.2143,0.0130,0.0083</t>
+  </si>
+  <si>
+    <t>0.7938,0.0124,0.0360,0.1505</t>
+  </si>
+  <si>
+    <t>0.9600,0.0335,0.0054,0.0016</t>
+  </si>
+  <si>
+    <t>0.0061,0.0987,0.9417,0.0251</t>
+  </si>
+  <si>
+    <t>0.7593,0.0013,0.1792,0.0270</t>
+  </si>
+  <si>
+    <t>0.8916,0.0240,0.0745,0.0177</t>
+  </si>
+  <si>
+    <t>0.7331,0.3051,0.0204,0.0037</t>
+  </si>
+  <si>
+    <t>0.5903,0.5045,0.0225,0.0051</t>
+  </si>
+  <si>
+    <t>0.5518,0.4933,0.0397,0.0014</t>
+  </si>
+  <si>
+    <t>0.1763,0.7914,0.0270,0.0360</t>
+  </si>
+  <si>
+    <t>0.8188,0.2583,0.0078,0.0014</t>
+  </si>
+  <si>
+    <t>0.3804,0.7129,0.0213,0.0009</t>
+  </si>
+  <si>
+    <t>0.9747,0.0075,0.0015,0.0055</t>
+  </si>
+  <si>
+    <t>0.9656,0.0302,0.0046,0.0022</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9843,0.0053,0.0039,0.0018</t>
+  </si>
+  <si>
+    <t>0.9785,0.0115,0.0046,0.0015</t>
+  </si>
+  <si>
+    <t>0.9608,0.0334,0.0072,0.0014</t>
+  </si>
+  <si>
+    <t>0.9837,0.0155,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9915,0.0042,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.3603,0.7609,0.0085,0.0020</t>
+  </si>
+  <si>
+    <t>0.5499,0.6192,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.3817,0.7344,0.0077,0.0007</t>
+  </si>
+  <si>
+    <t>0.2829,0.4835,0.3257,0.0030</t>
+  </si>
+  <si>
+    <t>0.9255,0.0866,0.0089,0.0031</t>
+  </si>
+  <si>
+    <t>0.5606,0.5995,0.0067,0.0014</t>
+  </si>
+  <si>
+    <t>0.9330,0.1120,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9832,0.0135,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.0288,0.9935,0.0009</t>
+  </si>
+  <si>
+    <t>0.9586,0.0396,0.0122,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.0059,0.9882,0.0044</t>
+  </si>
+  <si>
+    <t>0.0070,0.1913,0.9604,0.0046</t>
+  </si>
+  <si>
+    <t>0.0102,0.0027,0.9881,0.0031</t>
+  </si>
+  <si>
+    <t>0.0117,0.3270,0.9363,0.0018</t>
+  </si>
+  <si>
+    <t>0.0020,0.0060,0.9935,0.0010</t>
+  </si>
+  <si>
+    <t>0.0097,0.0119,0.9868,0.0004</t>
+  </si>
+  <si>
+    <t>0.0063,0.0064,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.4418,0.0442,0.6431,0.0107</t>
+  </si>
+  <si>
+    <t>0.3209,0.0983,0.6389,0.0122</t>
+  </si>
+  <si>
+    <t>0.5756,0.0634,0.4947,0.0221</t>
+  </si>
+  <si>
+    <t>0.3713,0.4187,0.1306,0.0009</t>
+  </si>
+  <si>
+    <t>0.1813,0.5991,0.2493,0.0029</t>
+  </si>
+  <si>
+    <t>0.5808,0.1906,0.2664,0.0157</t>
+  </si>
+  <si>
+    <t>0.4812,0.0504,0.5884,0.0216</t>
+  </si>
+  <si>
+    <t>0.1916,0.1422,0.6348,0.0034</t>
+  </si>
+  <si>
+    <t>0.8849,0.1987,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.1438,0.9128,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.5345,0.4933,0.0245,0.0004</t>
+  </si>
+  <si>
+    <t>0.9760,0.0498,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.8644,0.2293,0.0054,0.0004</t>
+  </si>
+  <si>
+    <t>0.3597,0.4178,0.1974,0.0023</t>
+  </si>
+  <si>
+    <t>0.8403,0.0176,0.2336,0.0025</t>
+  </si>
+  <si>
+    <t>0.3122,0.2836,0.0228,0.3446</t>
+  </si>
+  <si>
+    <t>0.8576,0.0114,0.1925,0.0037</t>
+  </si>
+  <si>
+    <t>0.6584,0.0243,0.4040,0.0177</t>
+  </si>
+  <si>
+    <t>0.0080,0.0126,0.9808,0.0058</t>
+  </si>
+  <si>
+    <t>0.0534,0.4365,0.6846,0.0467</t>
+  </si>
+  <si>
+    <t>0.0080,0.4764,0.8966,0.0048</t>
+  </si>
+  <si>
+    <t>0.0369,0.2250,0.8573,0.0040</t>
+  </si>
+  <si>
+    <t>0.0233,0.5392,0.7683,0.0034</t>
+  </si>
+  <si>
+    <t>0.9823,0.0139,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9870,0.0056,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.9876,0.0086,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9722,0.0219,0.0049,0.0012</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9769,0.0232,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9798,0.0237,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9714,0.0300,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.1139,0.0447,0.8802,0.0106</t>
+  </si>
+  <si>
+    <t>0.1203,0.5618,0.3536,0.0016</t>
+  </si>
+  <si>
+    <t>0.6825,0.0789,0.3222,0.0085</t>
+  </si>
+  <si>
+    <t>0.0023,0.0780,0.9877,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0046,0.9974,0.0011</t>
+  </si>
+  <si>
+    <t>0.0476,0.0339,0.9223,0.0107</t>
+  </si>
+  <si>
+    <t>0.0121,0.0458,0.9839,0.0002</t>
+  </si>
+  <si>
+    <t>0.0348,0.0898,0.8824,0.0033</t>
+  </si>
+  <si>
+    <t>0.0196,0.0221,0.9438,0.0236</t>
+  </si>
+  <si>
+    <t>0.0563,0.1824,0.7952,0.0124</t>
+  </si>
+  <si>
+    <t>0.0616,0.1372,0.7963,0.0102</t>
+  </si>
+  <si>
+    <t>0.4891,0.0060,0.6714,0.0084</t>
+  </si>
+  <si>
+    <t>0.5382,0.0073,0.6448,0.0072</t>
+  </si>
+  <si>
+    <t>0.8693,0.0215,0.0839,0.0144</t>
+  </si>
+  <si>
+    <t>0.9894,0.0074,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9786,0.0249,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9900,0.0108,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9775,0.0300,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9834,0.0283,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0119,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9851,0.0190,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9860,0.0171,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0201,0.1677,0.9307,0.0030</t>
+  </si>
+  <si>
+    <t>0.0040,0.5083,0.9349,0.0025</t>
+  </si>
+  <si>
+    <t>0.0124,0.1841,0.9106,0.0088</t>
+  </si>
+  <si>
+    <t>0.0322,0.0155,0.9447,0.0036</t>
+  </si>
+  <si>
+    <t>0.0158,0.0216,0.9706,0.0020</t>
+  </si>
+  <si>
+    <t>0.0390,0.0182,0.9141,0.1059</t>
+  </si>
+  <si>
+    <t>0.0495,0.0075,0.9478,0.0020</t>
+  </si>
+  <si>
+    <t>0.0474,0.0046,0.7509,0.2637</t>
+  </si>
+  <si>
+    <t>0.3957,0.0021,0.0053,0.7914</t>
+  </si>
+  <si>
+    <t>0.1792,0.0426,0.0260,0.8698</t>
+  </si>
+  <si>
+    <t>0.0144,0.0090,0.0060,0.9885</t>
+  </si>
+  <si>
+    <t>0.0031,0.0003,0.0023,0.9970</t>
+  </si>
+  <si>
+    <t>0.0222,0.0006,0.0004,0.9938</t>
+  </si>
+  <si>
+    <t>0.2095,0.1586,0.0059,0.7440</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2508,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4230,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,10 +4426,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5350,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
